--- a/data/dividends_info_20260630.xlsx
+++ b/data/dividends_info_20260630.xlsx
@@ -523,10 +523,10 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>64.95999908447266</v>
+        <v>64.48999786376953</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1385467999821949</v>
+        <v>0.1395565250135664</v>
       </c>
       <c r="J2" t="n">
         <v>258</v>
@@ -570,10 +570,10 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>64.65000152587891</v>
+        <v>65.19999694824219</v>
       </c>
       <c r="I3" t="n">
-        <v>1.082753261374318</v>
+        <v>1.073619682153792</v>
       </c>
       <c r="J3" t="n">
         <v>237</v>
@@ -617,10 +617,10 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>9.199999809265137</v>
+        <v>9.220000267028809</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6521739265643809</v>
+        <v>0.6507592002417079</v>
       </c>
       <c r="J4" t="n">
         <v>167</v>
@@ -711,10 +711,10 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>64.95999908447266</v>
+        <v>64.48999786376953</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1385467999821949</v>
+        <v>0.1395565250135664</v>
       </c>
       <c r="J6" t="n">
         <v>167</v>
@@ -758,10 +758,10 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>2.025000095367432</v>
+        <v>2.015000104904175</v>
       </c>
       <c r="I7" t="n">
-        <v>3.802468956725087</v>
+        <v>3.82133975142705</v>
       </c>
       <c r="J7" t="n">
         <v>146</v>
@@ -805,10 +805,10 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>20.55999946594238</v>
+        <v>20.6200008392334</v>
       </c>
       <c r="I8" t="n">
-        <v>1.313229606096317</v>
+        <v>1.309408288123222</v>
       </c>
       <c r="J8" t="n">
         <v>146</v>
@@ -852,10 +852,10 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>5.849999904632568</v>
+        <v>5.829999923706055</v>
       </c>
       <c r="I9" t="n">
-        <v>3.418803474537181</v>
+        <v>3.430531777311974</v>
       </c>
       <c r="J9" t="n">
         <v>139</v>
@@ -899,10 +899,10 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>7.650000095367432</v>
+        <v>7.599999904632568</v>
       </c>
       <c r="I10" t="n">
-        <v>0.7843137157126817</v>
+        <v>0.7894736941171157</v>
       </c>
       <c r="J10" t="n">
         <v>111</v>
@@ -1040,10 +1040,10 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>4.989999771118164</v>
+        <v>4.980000019073486</v>
       </c>
       <c r="I13" t="n">
-        <v>0.7615230810218038</v>
+        <v>0.7630522059128382</v>
       </c>
       <c r="J13" t="n">
         <v>90</v>
@@ -1087,10 +1087,10 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>20.55999946594238</v>
+        <v>20.6200008392334</v>
       </c>
       <c r="I14" t="n">
-        <v>1.313229606096317</v>
+        <v>1.309408288123222</v>
       </c>
       <c r="J14" t="n">
         <v>83</v>
@@ -1134,10 +1134,10 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>64.95999908447266</v>
+        <v>64.48999786376953</v>
       </c>
       <c r="I15" t="n">
-        <v>0.1385467999821949</v>
+        <v>0.1395565250135664</v>
       </c>
       <c r="J15" t="n">
         <v>83</v>
@@ -1275,10 +1275,10 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>4.989999771118164</v>
+        <v>4.980000019073486</v>
       </c>
       <c r="I18" t="n">
-        <v>0.7615230810218038</v>
+        <v>0.7630522059128382</v>
       </c>
       <c r="J18" t="n">
         <v>34</v>
@@ -1322,10 +1322,10 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>5.559999942779541</v>
+        <v>5.659999847412109</v>
       </c>
       <c r="I19" t="n">
-        <v>4.496402923972346</v>
+        <v>4.416961249818869</v>
       </c>
       <c r="J19" t="n">
         <v>27</v>
@@ -1369,10 +1369,10 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>4.130000114440918</v>
+        <v>4.199999809265137</v>
       </c>
       <c r="I20" t="n">
-        <v>3.38983041454351</v>
+        <v>3.333333484710216</v>
       </c>
       <c r="J20" t="n">
         <v>20</v>
@@ -1416,10 +1416,10 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>10.14999961853027</v>
+        <v>10.05399990081787</v>
       </c>
       <c r="I21" t="n">
-        <v>2.561576450952106</v>
+        <v>2.586035434303611</v>
       </c>
       <c r="J21" t="n">
         <v>20</v>
@@ -1463,10 +1463,10 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>14.81999969482422</v>
+        <v>14.73999977111816</v>
       </c>
       <c r="I22" t="n">
-        <v>4.04858307932048</v>
+        <v>4.070556372569635</v>
       </c>
       <c r="J22" t="n">
         <v>20</v>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>2.819999933242798</v>
+        <v>2.815999984741211</v>
       </c>
       <c r="I23" t="n">
-        <v>7.801418624397476</v>
+        <v>7.812500042332844</v>
       </c>
       <c r="J23" t="n">
         <v>20</v>
@@ -1604,10 +1604,10 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>6.644999980926514</v>
+        <v>6.614999771118164</v>
       </c>
       <c r="I25" t="n">
-        <v>3.611738159351157</v>
+        <v>3.628118039366639</v>
       </c>
       <c r="J25" t="n">
         <v>20</v>
@@ -1839,10 +1839,10 @@
         </is>
       </c>
       <c r="H30" t="n">
-        <v>2.279999971389771</v>
+        <v>2.200000047683716</v>
       </c>
       <c r="I30" t="n">
-        <v>3.728070222219713</v>
+        <v>3.863636279894303</v>
       </c>
       <c r="J30" t="n">
         <v>6</v>
@@ -1886,10 +1886,10 @@
         </is>
       </c>
       <c r="H31" t="n">
-        <v>4.75</v>
+        <v>4.739999771118164</v>
       </c>
       <c r="I31" t="n">
-        <v>1.473684210526316</v>
+        <v>1.476793320255521</v>
       </c>
       <c r="J31" t="n">
         <v>6</v>
@@ -1933,10 +1933,10 @@
         </is>
       </c>
       <c r="H32" t="n">
-        <v>34.04999923706055</v>
+        <v>33.95000076293945</v>
       </c>
       <c r="I32" t="n">
-        <v>0.4405286442319143</v>
+        <v>0.4418262050931769</v>
       </c>
       <c r="J32" t="n">
         <v>6</v>
@@ -1980,10 +1980,10 @@
         </is>
       </c>
       <c r="H33" t="n">
-        <v>4.920000076293945</v>
+        <v>5</v>
       </c>
       <c r="I33" t="n">
-        <v>0.8130081174740657</v>
+        <v>0.8</v>
       </c>
       <c r="J33" t="n">
         <v>-1</v>
@@ -2027,10 +2027,10 @@
         </is>
       </c>
       <c r="H34" t="n">
-        <v>21.45999908447266</v>
+        <v>21.71999931335449</v>
       </c>
       <c r="I34" t="n">
-        <v>1.164958111209273</v>
+        <v>1.151012927731945</v>
       </c>
       <c r="J34" t="n">
         <v>-8</v>
@@ -2074,10 +2074,10 @@
         </is>
       </c>
       <c r="H35" t="n">
-        <v>30.89999961853027</v>
+        <v>31.75</v>
       </c>
       <c r="I35" t="n">
-        <v>0.6310679689557711</v>
+        <v>0.6141732283464567</v>
       </c>
       <c r="J35" t="n">
         <v>-8</v>
@@ -2121,10 +2121,10 @@
         </is>
       </c>
       <c r="H36" t="n">
-        <v>1.860000014305115</v>
+        <v>1.879999995231628</v>
       </c>
       <c r="I36" t="n">
-        <v>1.774193534741913</v>
+        <v>1.755319153388305</v>
       </c>
       <c r="J36" t="n">
         <v>-8</v>
@@ -2168,10 +2168,10 @@
         </is>
       </c>
       <c r="H37" t="n">
-        <v>5.239999771118164</v>
+        <v>5.195000171661377</v>
       </c>
       <c r="I37" t="n">
-        <v>5.534351386777195</v>
+        <v>5.582290479641257</v>
       </c>
       <c r="J37" t="n">
         <v>-8</v>
@@ -2215,10 +2215,10 @@
         </is>
       </c>
       <c r="H38" t="n">
-        <v>3.664000034332275</v>
+        <v>3.651999950408936</v>
       </c>
       <c r="I38" t="n">
-        <v>4.366812186156496</v>
+        <v>4.381161067159486</v>
       </c>
       <c r="J38" t="n">
         <v>-8</v>
@@ -2262,10 +2262,10 @@
         </is>
       </c>
       <c r="H39" t="n">
-        <v>2.461999893188477</v>
+        <v>2.477999925613403</v>
       </c>
       <c r="I39" t="n">
-        <v>5.629569699960567</v>
+        <v>5.593220506884842</v>
       </c>
       <c r="J39" t="n">
         <v>-8</v>
@@ -2309,10 +2309,10 @@
         </is>
       </c>
       <c r="H40" t="n">
-        <v>47.06999969482422</v>
+        <v>46.92499923706055</v>
       </c>
       <c r="I40" t="n">
-        <v>1.338432131048589</v>
+        <v>1.342567949372361</v>
       </c>
       <c r="J40" t="n">
         <v>-8</v>
@@ -2356,10 +2356,10 @@
         </is>
       </c>
       <c r="H41" t="n">
-        <v>6.085000038146973</v>
+        <v>6.045000076293945</v>
       </c>
       <c r="I41" t="n">
-        <v>2.300739508994865</v>
+        <v>2.315963577056411</v>
       </c>
       <c r="J41" t="n">
         <v>-8</v>
@@ -2403,10 +2403,10 @@
         </is>
       </c>
       <c r="H42" t="n">
-        <v>16.64999961853027</v>
+        <v>16.5</v>
       </c>
       <c r="I42" t="n">
-        <v>4.684684792015942</v>
+        <v>4.727272727272728</v>
       </c>
       <c r="J42" t="n">
         <v>-8</v>
@@ -2450,10 +2450,10 @@
         </is>
       </c>
       <c r="H43" t="n">
-        <v>28.73999977111816</v>
+        <v>28.6200008392334</v>
       </c>
       <c r="I43" t="n">
-        <v>2.957550475884815</v>
+        <v>2.969950996069809</v>
       </c>
       <c r="J43" t="n">
         <v>-8</v>
@@ -2497,10 +2497,10 @@
         </is>
       </c>
       <c r="H44" t="n">
-        <v>64.95999908447266</v>
+        <v>64.48999786376953</v>
       </c>
       <c r="I44" t="n">
-        <v>0.1385467999821949</v>
+        <v>0.1395565250135664</v>
       </c>
       <c r="J44" t="n">
         <v>-8</v>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="H45" t="n">
-        <v>1.370000004768372</v>
+        <v>1.360000014305115</v>
       </c>
       <c r="I45" t="n">
-        <v>0.7299270047587131</v>
+        <v>0.7352941099128922</v>
       </c>
       <c r="J45" t="n">
         <v>-8</v>
@@ -2591,10 +2591,10 @@
         </is>
       </c>
       <c r="H46" t="n">
-        <v>6.331999778747559</v>
+        <v>6.315999984741211</v>
       </c>
       <c r="I46" t="n">
-        <v>2.863234465176503</v>
+        <v>2.870487657346448</v>
       </c>
       <c r="J46" t="n">
         <v>-8</v>
@@ -2638,10 +2638,10 @@
         </is>
       </c>
       <c r="H47" t="n">
-        <v>8.819999694824219</v>
+        <v>8.75</v>
       </c>
       <c r="I47" t="n">
-        <v>2.947845906985394</v>
+        <v>2.971428571428572</v>
       </c>
       <c r="J47" t="n">
         <v>-8</v>
@@ -2685,10 +2685,10 @@
         </is>
       </c>
       <c r="H48" t="n">
-        <v>10.3100004196167</v>
+        <v>10.23999977111816</v>
       </c>
       <c r="I48" t="n">
-        <v>2.686711820815796</v>
+        <v>2.70507818546321</v>
       </c>
       <c r="J48" t="n">
         <v>-8</v>
@@ -2732,10 +2732,10 @@
         </is>
       </c>
       <c r="H49" t="n">
-        <v>0.9879999756813049</v>
+        <v>0.9959999918937683</v>
       </c>
       <c r="I49" t="n">
-        <v>1.366396794766181</v>
+        <v>1.355421697778476</v>
       </c>
       <c r="J49" t="n">
         <v>-15</v>
@@ -2779,10 +2779,10 @@
         </is>
       </c>
       <c r="H50" t="n">
-        <v>3.019999980926514</v>
+        <v>2.977999925613403</v>
       </c>
       <c r="I50" t="n">
-        <v>3.642384128964558</v>
+        <v>3.693754289713167</v>
       </c>
       <c r="J50" t="n">
         <v>-15</v>
@@ -2826,10 +2826,10 @@
         </is>
       </c>
       <c r="H51" t="n">
-        <v>1.620000004768372</v>
+        <v>1.690000057220459</v>
       </c>
       <c r="I51" t="n">
-        <v>1.481481477120831</v>
+        <v>1.420118295112532</v>
       </c>
       <c r="J51" t="n">
         <v>-15</v>
@@ -2873,10 +2873,10 @@
         </is>
       </c>
       <c r="H52" t="n">
-        <v>2.950000047683716</v>
+        <v>2.940000057220459</v>
       </c>
       <c r="I52" t="n">
-        <v>5.423728725890325</v>
+        <v>5.442176764828622</v>
       </c>
       <c r="J52" t="n">
         <v>-22</v>
@@ -2920,10 +2920,10 @@
         </is>
       </c>
       <c r="H53" t="n">
-        <v>0.8450000286102295</v>
+        <v>0.8650000095367432</v>
       </c>
       <c r="I53" t="n">
-        <v>2.958579781484442</v>
+        <v>2.890173378540068</v>
       </c>
       <c r="J53" t="n">
         <v>-22</v>
@@ -2967,10 +2967,10 @@
         </is>
       </c>
       <c r="H54" t="n">
-        <v>27.5</v>
+        <v>27.29999923706055</v>
       </c>
       <c r="I54" t="n">
-        <v>4.036363636363636</v>
+        <v>4.065934179562696</v>
       </c>
       <c r="J54" t="n">
         <v>-26</v>
@@ -3013,12 +3013,8 @@
           <t>IT0001237053</t>
         </is>
       </c>
-      <c r="H55" t="n">
-        <v>0.875</v>
-      </c>
-      <c r="I55" t="n">
-        <v>3.428571428571429</v>
-      </c>
+      <c r="H55" t="inlineStr"/>
+      <c r="I55" t="inlineStr"/>
       <c r="J55" t="n">
         <v>-29</v>
       </c>
@@ -3061,10 +3057,10 @@
         </is>
       </c>
       <c r="H56" t="n">
-        <v>0.4620000123977661</v>
+        <v>0.4589999914169312</v>
       </c>
       <c r="I56" t="n">
-        <v>4.978354844760868</v>
+        <v>5.010893339888545</v>
       </c>
       <c r="J56" t="n">
         <v>-29</v>
@@ -3155,10 +3151,10 @@
         </is>
       </c>
       <c r="H58" t="n">
-        <v>8.979999542236328</v>
+        <v>9</v>
       </c>
       <c r="I58" t="n">
-        <v>2.227171605736999</v>
+        <v>2.222222222222222</v>
       </c>
       <c r="J58" t="n">
         <v>-29</v>
@@ -5003,7 +4999,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>ASCOPIAVE S.p.A.</t>
+          <t>CASTELLO SGR S.p.A.</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -5020,7 +5016,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Prysmian S.p.A.</t>
+          <t>ENEL S.p.A.</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -5030,14 +5026,14 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Pozzi Milano S.p.A.</t>
+          <t>ENEL S.p.A.</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -5047,14 +5043,14 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>BRUNELLO CUCINELLI S.p.A.</t>
+          <t>ELICA S.p.A.</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -5071,7 +5067,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>BRUNELLO CUCINELLI S.p.A.</t>
+          <t>DEA CAPITAL REAL ESTATE SGR S.p.A.</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -5081,14 +5077,14 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Alerion Clean Power S.p.A.</t>
+          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -5098,14 +5094,14 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>BANCA MEDIOLANUM S.p.A.</t>
+          <t>DE' LONGHI S.p.A.</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -5122,7 +5118,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>AZIMUT HOLDING S.p.A.</t>
+          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -5139,7 +5135,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>ASCOPIAVE S.p.A.</t>
+          <t>COMPAGNIA DEI CARAIBI S.p.A.</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -5149,14 +5145,14 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>RAI WAY S.p.A.</t>
+          <t>ESAUTOMOTION S.p.A.</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -5166,14 +5162,14 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>BANCO DI DESIO E DELLA BRIANZA S.p.A.</t>
+          <t>DE' LONGHI S.p.A.</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -5183,14 +5179,14 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>RCS MediaGroup S.p.A.</t>
+          <t>Ferrari N.V.</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -5207,7 +5203,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>CALTAGIRONE S.p.A.</t>
+          <t>Prysmian S.p.A.</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -5217,14 +5213,14 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>SOGES GROUP S.p.A.</t>
+          <t>FinecoBank S.p.A.</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -5234,14 +5230,14 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Stellantis N.V.</t>
+          <t>First Capital S.p.A.</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -5251,14 +5247,14 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Stellantis N.V.</t>
+          <t>Gabetti Property Solutions S.p.A.</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -5268,14 +5264,14 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>TECHNOGYM S.p.A.</t>
+          <t>IREN S.p.A.</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -5292,7 +5288,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>TECHNOGYM S.p.A.</t>
+          <t>Industrie De Nora S.p.A.</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -5302,14 +5298,14 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Banca Profilo S.p.A.</t>
+          <t>Pozzi Milano S.p.A.</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -5319,14 +5315,14 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
+          <t>CALTAGIRONE S.p.A.</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -5336,14 +5332,14 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>CASTELLO SGR S.p.A.</t>
+          <t>RAI WAY S.p.A.</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -5360,7 +5356,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>COMPAGNIA DEI CARAIBI S.p.A.</t>
+          <t>RCS MediaGroup S.p.A.</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -5370,14 +5366,14 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
+          <t>REPLY S.p.A.</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -5394,7 +5390,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
+          <t>SOGES GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -5404,14 +5400,14 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>DE' LONGHI S.p.A.</t>
+          <t>Stellantis N.V.</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -5428,7 +5424,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>DE' LONGHI S.p.A.</t>
+          <t>Stellantis N.V.</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -5445,7 +5441,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>REPLY S.p.A.</t>
+          <t>Ferrari N.V.</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -5455,14 +5451,14 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
+          <t>Banca Profilo S.p.A.</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -5479,7 +5475,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Iveco Group N.V.</t>
+          <t>ASCOPIAVE S.p.A.</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -5496,7 +5492,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>MAIRE S.p.A.</t>
+          <t>BRUNELLO CUCINELLI S.p.A.</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -5513,7 +5509,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>DEA CAPITAL REAL ESTATE SGR S.p.A.</t>
+          <t>TECHNOGYM S.p.A.</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -5598,7 +5594,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>TELECOM ITALIA S.p.A.</t>
+          <t>Industrie De Nora S.p.A.</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -5615,7 +5611,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Toscana Aeroporti S.p.A.</t>
+          <t>Intred S.p.A.</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -5632,7 +5628,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>VALTECNE S.p.A.</t>
+          <t>Iveco Group N.V.</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -5642,14 +5638,14 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>ZIGNAGO VETRO S.p.A.</t>
+          <t>KALEON S.P.A.</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -5659,14 +5655,14 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>ENEL S.p.A.</t>
+          <t>Kruso Kapital S.p.A.</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -5676,14 +5672,14 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>ENEL S.p.A.</t>
+          <t>Leonardo S.p.A.</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -5700,7 +5696,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>ESAUTOMOTION S.p.A.</t>
+          <t>Lottomatica Group S.p.A.</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -5710,14 +5706,14 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Misitano &amp; Stracuzzi S.p.A.</t>
+          <t>BRUNELLO CUCINELLI S.p.A.</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -5727,14 +5723,14 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Ferrari N.V.</t>
+          <t>MAIRE S.p.A.</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -5751,7 +5747,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>FinecoBank S.p.A.</t>
+          <t>Misitano &amp; Stracuzzi S.p.A.</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -5761,14 +5757,14 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>First Capital S.p.A.</t>
+          <t>TELECOM ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -5778,14 +5774,14 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Gabetti Property Solutions S.p.A.</t>
+          <t>Toscana Aeroporti S.p.A.</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -5795,14 +5791,14 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>IREN S.p.A.</t>
+          <t>VALTECNE S.p.A.</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -5812,14 +5808,14 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Industrie De Nora S.p.A.</t>
+          <t>ZIGNAGO VETRO S.p.A.</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -5836,7 +5832,7 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Industrie De Nora S.p.A.</t>
+          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -5846,14 +5842,14 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Intred S.p.A.</t>
+          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -5863,14 +5859,14 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>KALEON S.P.A.</t>
+          <t>ASCOPIAVE S.p.A.</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -5880,14 +5876,14 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Kruso Kapital S.p.A.</t>
+          <t>AZIMUT HOLDING S.p.A.</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -5904,7 +5900,7 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Leonardo S.p.A.</t>
+          <t>Alerion Clean Power S.p.A.</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -5921,7 +5917,7 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Lottomatica Group S.p.A.</t>
+          <t>BANCA MEDIOLANUM S.p.A.</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -5931,14 +5927,14 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>MAIRE S.p.A.</t>
+          <t>BANCO DI DESIO E DELLA BRIANZA S.p.A.</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -5955,7 +5951,7 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Ferrari N.V.</t>
+          <t>MAIRE S.p.A.</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -5972,7 +5968,7 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>ELICA S.p.A.</t>
+          <t>TECHNOGYM S.p.A.</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -5982,7 +5978,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -6010,1013 +6006,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C59"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Stock</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>A2A S.p.A.</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>AEDES S.p.A.</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>AMPLIFON S.p.A.</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>AMPLIFON S.p.A.</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>ASCOPIAVE S.p.A.</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>ASCOPIAVE S.p.A.</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>AZIMUT HOLDING S.p.A.</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Alerion Clean Power S.p.A.</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>BANCA MEDIOLANUM S.p.A.</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>BANCO DI DESIO E DELLA BRIANZA S.p.A.</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>BRUNELLO CUCINELLI S.p.A.</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>BRUNELLO CUCINELLI S.p.A.</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Banca Profilo S.p.A.</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>CALTAGIRONE S.p.A.</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>CASTELLO SGR S.p.A.</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>COMPAGNIA DEI CARAIBI S.p.A.</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Half Year Preliminary Results</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>DE' LONGHI S.p.A.</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>DE' LONGHI S.p.A.</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>DEA CAPITAL REAL ESTATE SGR S.p.A.</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>ELICA S.p.A.</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>ENEL S.p.A.</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>ENEL S.p.A.</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>ESAUTOMOTION S.p.A.</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Half Year Preliminary Results</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Ferrari N.V.</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Ferrari N.V.</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>FinecoBank S.p.A.</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>First Capital S.p.A.</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Half Year Preliminary Results</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Gabetti Property Solutions S.p.A.</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>IREN S.p.A.</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>Industrie De Nora S.p.A.</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>Industrie De Nora S.p.A.</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>Intred S.p.A.</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Half Year Preliminary Results</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>Iveco Group N.V.</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>KALEON S.P.A.</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Half Year Preliminary Results</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>Kruso Kapital S.p.A.</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>Leonardo S.p.A.</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>Lottomatica Group S.p.A.</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>MAIRE S.p.A.</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>MAIRE S.p.A.</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>Misitano &amp; Stracuzzi S.p.A.</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>Pozzi Milano S.p.A.</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Half Year Preliminary Results</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>Prysmian S.p.A.</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>RAI WAY S.p.A.</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>RCS MediaGroup S.p.A.</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>REPLY S.p.A.</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>SOGES GROUP S.p.A.</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Half Year Preliminary Results</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>Stellantis N.V.</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>Stellantis N.V.</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>TECHNOGYM S.p.A.</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>TECHNOGYM S.p.A.</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>TELECOM ITALIA S.p.A.</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>Toscana Aeroporti S.p.A.</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Half Year Preliminary Results</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>VALTECNE S.p.A.</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Half Year Preliminary Results</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>ZIGNAGO VETRO S.p.A.</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>